--- a/artfynd/A 24431-2024 artfynd.xlsx
+++ b/artfynd/A 24431-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,1089 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118983305</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549467</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7027516</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118983297</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7027536</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118983303</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549455</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7027638</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118983307</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549312</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027469</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118983304</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549533</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027598</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118983309</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>549420</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7027633</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118983308</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>549402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7027602</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118983299</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>549476</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7027555</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118983306</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>549304</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7027444</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118983298</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>549476</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7027539</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24431-2024 artfynd.xlsx
+++ b/artfynd/A 24431-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118983305</v>
+        <v>118983309</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549467</v>
+        <v>549420</v>
       </c>
       <c r="R7" t="n">
-        <v>7027516</v>
+        <v>7027633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118983297</v>
+        <v>118983307</v>
       </c>
       <c r="B8" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,34 +1362,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549473</v>
+        <v>549312</v>
       </c>
       <c r="R8" t="n">
-        <v>7027536</v>
+        <v>7027469</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1426,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118983303</v>
+        <v>118983306</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1492,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549455</v>
+        <v>549304</v>
       </c>
       <c r="R9" t="n">
-        <v>7027638</v>
+        <v>7027444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1541,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118983307</v>
+        <v>118983298</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,38 +1584,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549312</v>
+        <v>549476</v>
       </c>
       <c r="R10" t="n">
-        <v>7027469</v>
+        <v>7027539</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,11 +1644,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1670,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118983304</v>
+        <v>118983305</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549533</v>
+        <v>549467</v>
       </c>
       <c r="R11" t="n">
-        <v>7027598</v>
+        <v>7027516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118983309</v>
+        <v>118983303</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549420</v>
+        <v>549455</v>
       </c>
       <c r="R12" t="n">
-        <v>7027633</v>
+        <v>7027638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118983306</v>
+        <v>118983297</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,38 +2121,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549304</v>
+        <v>549473</v>
       </c>
       <c r="R15" t="n">
-        <v>7027444</v>
+        <v>7027536</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,11 +2181,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118983298</v>
+        <v>118983304</v>
       </c>
       <c r="B16" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,34 +2223,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549476</v>
+        <v>549533</v>
       </c>
       <c r="R16" t="n">
-        <v>7027539</v>
+        <v>7027598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,6 +2287,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 24431-2024 artfynd.xlsx
+++ b/artfynd/A 24431-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103986803</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549640.7286941414</v>
+        <v>549641</v>
       </c>
       <c r="R2" t="n">
-        <v>7027539.036817946</v>
+        <v>7027539</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>103986808</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549479.6096426868</v>
+        <v>549480</v>
       </c>
       <c r="R3" t="n">
-        <v>7027557.183479739</v>
+        <v>7027557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>103986804</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549625.5798329811</v>
+        <v>549626</v>
       </c>
       <c r="R4" t="n">
-        <v>7027559.889306303</v>
+        <v>7027560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103986805</v>
+        <v>118983297</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Köttsjön, Jmt</t>
+          <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549603.5709803985</v>
+        <v>549473</v>
       </c>
       <c r="R5" t="n">
-        <v>7027559.548553208</v>
+        <v>7027536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103986807</v>
+        <v>118983298</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Köttsjön, Jmt</t>
+          <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549603.5709803985</v>
+        <v>549476</v>
       </c>
       <c r="R6" t="n">
-        <v>7027559.548553208</v>
+        <v>7027539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118983306</v>
+        <v>118983299</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,38 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549304</v>
+        <v>549476</v>
       </c>
       <c r="R7" t="n">
-        <v>7027444</v>
+        <v>7027555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118983299</v>
+        <v>103986805</v>
       </c>
       <c r="B8" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskhusberget, Jmt</t>
+          <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549476</v>
+        <v>549604</v>
       </c>
       <c r="R8" t="n">
-        <v>7027555</v>
+        <v>7027560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118983305</v>
+        <v>103986807</v>
       </c>
       <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,38 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskhusberget, Jmt</t>
+          <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549467</v>
+        <v>549604</v>
       </c>
       <c r="R9" t="n">
-        <v>7027516</v>
+        <v>7027560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118983298</v>
+        <v>118983303</v>
       </c>
       <c r="B10" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,34 +1462,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549476</v>
+        <v>549455</v>
       </c>
       <c r="R10" t="n">
-        <v>7027539</v>
+        <v>7027638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,6 +1526,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118983307</v>
+        <v>118983304</v>
       </c>
       <c r="B11" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549312</v>
+        <v>549533</v>
       </c>
       <c r="R11" t="n">
-        <v>7027469</v>
+        <v>7027598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,15 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118983309</v>
+        <v>118983305</v>
       </c>
       <c r="B12" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549420</v>
+        <v>549467</v>
       </c>
       <c r="R12" t="n">
-        <v>7027633</v>
+        <v>7027516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,15 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118983304</v>
+        <v>118983306</v>
       </c>
       <c r="B13" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549533</v>
+        <v>549304</v>
       </c>
       <c r="R13" t="n">
-        <v>7027598</v>
+        <v>7027444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,15 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118983308</v>
+        <v>118983307</v>
       </c>
       <c r="B14" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549402</v>
+        <v>549312</v>
       </c>
       <c r="R14" t="n">
-        <v>7027602</v>
+        <v>7027469</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,15 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118983303</v>
+        <v>118983308</v>
       </c>
       <c r="B15" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549455</v>
+        <v>549402</v>
       </c>
       <c r="R15" t="n">
-        <v>7027638</v>
+        <v>7027602</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,7 +2060,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,15 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118983297</v>
+        <v>118983309</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,34 +2098,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549473</v>
+        <v>549420</v>
       </c>
       <c r="R16" t="n">
-        <v>7027536</v>
+        <v>7027633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 24431-2024 artfynd.xlsx
+++ b/artfynd/A 24431-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986803</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986804</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983297</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983299</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986805</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986807</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983303</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,8 +2265,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983309</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>